--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/52.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/52.xlsx
@@ -426,13 +426,13 @@
         <v>-0.05011661676827701</v>
       </c>
       <c r="E2">
-        <v>-5.9960231845177</v>
+        <v>-8.838315366957993</v>
       </c>
       <c r="F2">
-        <v>-8.424163969113707</v>
+        <v>-8.258245831103258</v>
       </c>
       <c r="G2">
-        <v>-6.410915624558998</v>
+        <v>-8.22172444472063</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>0.3040192035216122</v>
       </c>
       <c r="E3">
-        <v>-6.158758426457342</v>
+        <v>-8.97312350969233</v>
       </c>
       <c r="F3">
-        <v>-8.14556159188143</v>
+        <v>-7.943940387713313</v>
       </c>
       <c r="G3">
-        <v>-6.246662907628059</v>
+        <v>-8.065638843635073</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>0.4802681182943813</v>
       </c>
       <c r="E4">
-        <v>-7.176279365136825</v>
+        <v>-9.654781116644926</v>
       </c>
       <c r="F4">
-        <v>-8.216397194140727</v>
+        <v>-7.725698585889138</v>
       </c>
       <c r="G4">
-        <v>-6.062162894178936</v>
+        <v>-8.754960635822119</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>0.4423288592124974</v>
       </c>
       <c r="E5">
-        <v>-7.823746993331509</v>
+        <v>-9.170818570971187</v>
       </c>
       <c r="F5">
-        <v>-8.149922722046073</v>
+        <v>-8.237176603530729</v>
       </c>
       <c r="G5">
-        <v>-6.518594428769333</v>
+        <v>-8.35436476229707</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>0.236702236163304</v>
       </c>
       <c r="E6">
-        <v>-8.02837514831611</v>
+        <v>-10.09597675379023</v>
       </c>
       <c r="F6">
-        <v>-7.962133605343404</v>
+        <v>-7.712030411985938</v>
       </c>
       <c r="G6">
-        <v>-6.517535054196766</v>
+        <v>-9.214033985752854</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.09476541555955857</v>
       </c>
       <c r="E7">
-        <v>-8.462877700878073</v>
+        <v>-9.121883880844303</v>
       </c>
       <c r="F7">
-        <v>-7.999953294457055</v>
+        <v>-7.368201522920372</v>
       </c>
       <c r="G7">
-        <v>-7.016096591319928</v>
+        <v>-9.128966207575742</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.4907688044038666</v>
       </c>
       <c r="E8">
-        <v>-9.43109714303605</v>
+        <v>-11.08014548140322</v>
       </c>
       <c r="F8">
-        <v>-7.975635490125482</v>
+        <v>-7.677252230082888</v>
       </c>
       <c r="G8">
-        <v>-8.096572581154023</v>
+        <v>-10.10036634298193</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.8914248717322639</v>
       </c>
       <c r="E9">
-        <v>-10.44709198597495</v>
+        <v>-12.19518710783788</v>
       </c>
       <c r="F9">
-        <v>-7.617448327304063</v>
+        <v>-7.673395510252313</v>
       </c>
       <c r="G9">
-        <v>-7.926129144064646</v>
+        <v>-9.542930063988369</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.236435074108456</v>
       </c>
       <c r="E10">
-        <v>-10.67186279334567</v>
+        <v>-12.48577475643608</v>
       </c>
       <c r="F10">
-        <v>-7.62938828212704</v>
+        <v>-7.281804822262447</v>
       </c>
       <c r="G10">
-        <v>-7.939205798944767</v>
+        <v>-9.948985027107677</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.478581147545884</v>
       </c>
       <c r="E11">
-        <v>-10.66624748557616</v>
+        <v>-12.43760537841649</v>
       </c>
       <c r="F11">
-        <v>-7.170961245240839</v>
+        <v>-7.690265145663575</v>
       </c>
       <c r="G11">
-        <v>-8.691580241472773</v>
+        <v>-10.53045917726189</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.586156716372444</v>
       </c>
       <c r="E12">
-        <v>-10.77653847003297</v>
+        <v>-13.3113834951445</v>
       </c>
       <c r="F12">
-        <v>-7.416623727211412</v>
+        <v>-7.437351666159163</v>
       </c>
       <c r="G12">
-        <v>-8.993876086300242</v>
+        <v>-11.18502686237766</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.547873249917392</v>
       </c>
       <c r="E13">
-        <v>-11.42997462696976</v>
+        <v>-13.75067717320658</v>
       </c>
       <c r="F13">
-        <v>-7.149184101124111</v>
+        <v>-7.024149727247209</v>
       </c>
       <c r="G13">
-        <v>-9.351878480917028</v>
+        <v>-10.89805884339702</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.371445811148036</v>
       </c>
       <c r="E14">
-        <v>-11.97218693380416</v>
+        <v>-14.67574931501947</v>
       </c>
       <c r="F14">
-        <v>-6.973428773819908</v>
+        <v>-6.952483867161742</v>
       </c>
       <c r="G14">
-        <v>-8.844193080287635</v>
+        <v>-10.69690678588536</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.082345142173003</v>
       </c>
       <c r="E15">
-        <v>-13.44832454913645</v>
+        <v>-14.08593821789045</v>
       </c>
       <c r="F15">
-        <v>-6.81163539786622</v>
+        <v>-6.688033881916311</v>
       </c>
       <c r="G15">
-        <v>-8.368523965568533</v>
+        <v>-9.72089506054297</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.7198109204590732</v>
       </c>
       <c r="E16">
-        <v>-13.2848738083036</v>
+        <v>-13.91517852000921</v>
       </c>
       <c r="F16">
-        <v>-6.551650275522891</v>
+        <v>-6.947069572563334</v>
       </c>
       <c r="G16">
-        <v>-8.036492800707329</v>
+        <v>-9.327873715211773</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.3321102660187301</v>
       </c>
       <c r="E17">
-        <v>-13.02440504033042</v>
+        <v>-15.72056789501719</v>
       </c>
       <c r="F17">
-        <v>-6.199054386435932</v>
+        <v>-6.262164671239715</v>
       </c>
       <c r="G17">
-        <v>-7.988105867105341</v>
+        <v>-9.223634567816742</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.02939646581663166</v>
       </c>
       <c r="E18">
-        <v>-13.60352893880134</v>
+        <v>-17.78499051173793</v>
       </c>
       <c r="F18">
-        <v>-6.024170097385221</v>
+        <v>-5.995787711821673</v>
       </c>
       <c r="G18">
-        <v>-7.831805080559731</v>
+        <v>-8.803215147602536</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.3182629861054088</v>
       </c>
       <c r="E19">
-        <v>-15.66091430691415</v>
+        <v>-17.20843878650336</v>
       </c>
       <c r="F19">
-        <v>-5.299266723534784</v>
+        <v>-5.58535290307047</v>
       </c>
       <c r="G19">
-        <v>-7.369338421451243</v>
+        <v>-7.739775225113531</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.4960859000235708</v>
       </c>
       <c r="E20">
-        <v>-15.84759611940636</v>
+        <v>-18.47657906218934</v>
       </c>
       <c r="F20">
-        <v>-5.009254537034725</v>
+        <v>-5.388518845958248</v>
       </c>
       <c r="G20">
-        <v>-6.915343448377749</v>
+        <v>-8.353166344811854</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.5400248271522113</v>
       </c>
       <c r="E21">
-        <v>-17.19649720054513</v>
+        <v>-18.54743609498736</v>
       </c>
       <c r="F21">
-        <v>-4.796762379536552</v>
+        <v>-5.03882866129964</v>
       </c>
       <c r="G21">
-        <v>-6.784994028314485</v>
+        <v>-8.549147330191168</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.4383551841059803</v>
       </c>
       <c r="E22">
-        <v>-17.67636147724193</v>
+        <v>-18.50768515014803</v>
       </c>
       <c r="F22">
-        <v>-4.221271364719377</v>
+        <v>-4.527318573613262</v>
       </c>
       <c r="G22">
-        <v>-6.613699781021515</v>
+        <v>-8.036297478520511</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.1978684518672263</v>
       </c>
       <c r="E23">
-        <v>-18.13698879635414</v>
+        <v>-20.2136473498436</v>
       </c>
       <c r="F23">
-        <v>-4.252372973339734</v>
+        <v>-4.438951742796529</v>
       </c>
       <c r="G23">
-        <v>-6.025326453963465</v>
+        <v>-7.304153779782993</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.1643873607721583</v>
       </c>
       <c r="E24">
-        <v>-18.253212081761</v>
+        <v>-20.33661806152189</v>
       </c>
       <c r="F24">
-        <v>-3.867496010651894</v>
+        <v>-4.274453793065749</v>
       </c>
       <c r="G24">
-        <v>-6.297446676200479</v>
+        <v>-8.131876238784811</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.6182553961599172</v>
       </c>
       <c r="E25">
-        <v>-19.44938584851709</v>
+        <v>-21.66959249957569</v>
       </c>
       <c r="F25">
-        <v>-3.88158228291677</v>
+        <v>-3.737189479782494</v>
       </c>
       <c r="G25">
-        <v>-6.877292037949366</v>
+        <v>-8.25415785936887</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.129174241647358</v>
       </c>
       <c r="E26">
-        <v>-18.82305713699021</v>
+        <v>-21.54508210673479</v>
       </c>
       <c r="F26">
-        <v>-3.580253725797937</v>
+        <v>-3.760550725741141</v>
       </c>
       <c r="G26">
-        <v>-8.019622260639203</v>
+        <v>-8.222151505095196</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.658197984487173</v>
       </c>
       <c r="E27">
-        <v>-19.00631995160662</v>
+        <v>-20.67023527014097</v>
       </c>
       <c r="F27">
-        <v>-4.028479716956314</v>
+        <v>-4.105892053955952</v>
       </c>
       <c r="G27">
-        <v>-7.357192029867656</v>
+        <v>-8.271326348535531</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.167539100929309</v>
       </c>
       <c r="E28">
-        <v>-19.01085748256231</v>
+        <v>-20.00392919007438</v>
       </c>
       <c r="F28">
-        <v>-3.944648619881399</v>
+        <v>-3.859778611725957</v>
       </c>
       <c r="G28">
-        <v>-8.240392611016581</v>
+        <v>-8.24906955087501</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.621271982976467</v>
       </c>
       <c r="E29">
-        <v>-18.34048936131083</v>
+        <v>-19.77921272439175</v>
       </c>
       <c r="F29">
-        <v>-3.728138600475757</v>
+        <v>-3.819842299656321</v>
       </c>
       <c r="G29">
-        <v>-7.517382707421911</v>
+        <v>-9.254998676255797</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.988628986510701</v>
       </c>
       <c r="E30">
-        <v>-18.82346017117689</v>
+        <v>-20.08016604999351</v>
       </c>
       <c r="F30">
-        <v>-3.331089274121849</v>
+        <v>-3.833814545095285</v>
       </c>
       <c r="G30">
-        <v>-7.343314222967032</v>
+        <v>-8.84363028754596</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.245054326957291</v>
       </c>
       <c r="E31">
-        <v>-18.95011706069743</v>
+        <v>-21.81370665639579</v>
       </c>
       <c r="F31">
-        <v>-3.534628742080042</v>
+        <v>-4.262620342465586</v>
       </c>
       <c r="G31">
-        <v>-7.909523447639661</v>
+        <v>-8.554195912138557</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.374396503856161</v>
       </c>
       <c r="E32">
-        <v>-18.0829459875466</v>
+        <v>-20.20764259330943</v>
       </c>
       <c r="F32">
-        <v>-3.689357601871434</v>
+        <v>-3.918093830944269</v>
       </c>
       <c r="G32">
-        <v>-7.801993617978594</v>
+        <v>-8.47700723234491</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.367452038990237</v>
       </c>
       <c r="E33">
-        <v>-17.87955863444011</v>
+        <v>-19.80967576904135</v>
       </c>
       <c r="F33">
-        <v>-3.741541503638121</v>
+        <v>-4.286865296325048</v>
       </c>
       <c r="G33">
-        <v>-7.763707158816922</v>
+        <v>-8.080715068020913</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.223870315332837</v>
       </c>
       <c r="E34">
-        <v>-19.39989415608726</v>
+        <v>-20.53550411146476</v>
       </c>
       <c r="F34">
-        <v>-3.860269560559744</v>
+        <v>-3.884844717102575</v>
       </c>
       <c r="G34">
-        <v>-6.930184624030302</v>
+        <v>-8.766805767761632</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.947787124313261</v>
       </c>
       <c r="E35">
-        <v>-18.41359704569066</v>
+        <v>-19.65497403999132</v>
       </c>
       <c r="F35">
-        <v>-3.610664046786205</v>
+        <v>-4.348558560260992</v>
       </c>
       <c r="G35">
-        <v>-6.991823671425992</v>
+        <v>-9.037929515791324</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.552983350904785</v>
       </c>
       <c r="E36">
-        <v>-17.50188843067441</v>
+        <v>-20.1626974887833</v>
       </c>
       <c r="F36">
-        <v>-4.15828421305052</v>
+        <v>-4.295300114030678</v>
       </c>
       <c r="G36">
-        <v>-7.203215246290614</v>
+        <v>-8.690345407986625</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.052178662721943</v>
       </c>
       <c r="E37">
-        <v>-18.11106781113424</v>
+        <v>-20.02274047110224</v>
       </c>
       <c r="F37">
-        <v>-4.075636936147396</v>
+        <v>-4.358656269177834</v>
       </c>
       <c r="G37">
-        <v>-6.300416235549204</v>
+        <v>-7.753434536008564</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.468724038501231</v>
       </c>
       <c r="E38">
-        <v>-17.87053791421683</v>
+        <v>-18.63748480062988</v>
       </c>
       <c r="F38">
-        <v>-3.984589683068783</v>
+        <v>-4.477872899374369</v>
       </c>
       <c r="G38">
-        <v>-6.518332895671731</v>
+        <v>-8.022866595267688</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.8198133025832939</v>
       </c>
       <c r="E39">
-        <v>-17.18229590605708</v>
+        <v>-19.42274483592997</v>
       </c>
       <c r="F39">
-        <v>-3.70871523927585</v>
+        <v>-4.520972664010095</v>
       </c>
       <c r="G39">
-        <v>-6.812157054464206</v>
+        <v>-6.59855403517935</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.1322554926121949</v>
       </c>
       <c r="E40">
-        <v>-16.64640082046338</v>
+        <v>-18.31973989340769</v>
       </c>
       <c r="F40">
-        <v>-3.958719846940079</v>
+        <v>-4.179138452545025</v>
       </c>
       <c r="G40">
-        <v>-6.768275773341165</v>
+        <v>-6.047675946899085</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.5773524859631767</v>
       </c>
       <c r="E41">
-        <v>-17.04199019587743</v>
+        <v>-19.41188102678557</v>
       </c>
       <c r="F41">
-        <v>-3.814860752699306</v>
+        <v>-4.247198214261036</v>
       </c>
       <c r="G41">
-        <v>-6.629457977788446</v>
+        <v>-7.186775077142594</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.285364493109552</v>
       </c>
       <c r="E42">
-        <v>-16.35878837928822</v>
+        <v>-17.83312819043946</v>
       </c>
       <c r="F42">
-        <v>-4.016489479470522</v>
+        <v>-4.49528099479688</v>
       </c>
       <c r="G42">
-        <v>-6.607062137215276</v>
+        <v>-6.506722812465506</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.978766306304183</v>
       </c>
       <c r="E43">
-        <v>-15.86841351441962</v>
+        <v>-17.59335907715534</v>
       </c>
       <c r="F43">
-        <v>-4.010059633453837</v>
+        <v>-4.312198256148418</v>
       </c>
       <c r="G43">
-        <v>-6.104418697442193</v>
+        <v>-6.495824496550226</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.639022766338293</v>
       </c>
       <c r="E44">
-        <v>-15.45244147749704</v>
+        <v>-16.95683677063719</v>
       </c>
       <c r="F44">
-        <v>-4.127428078847055</v>
+        <v>-4.542609254226829</v>
       </c>
       <c r="G44">
-        <v>-6.24506391413259</v>
+        <v>-6.031851539221369</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>3.253679191039134</v>
       </c>
       <c r="E45">
-        <v>-15.65370950476795</v>
+        <v>-17.32496547966873</v>
       </c>
       <c r="F45">
-        <v>-4.346746800693729</v>
+        <v>-4.447670043861023</v>
       </c>
       <c r="G45">
-        <v>-5.495331286944923</v>
+        <v>-6.004393874518653</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>3.810140309426704</v>
       </c>
       <c r="E46">
-        <v>-14.66642065856367</v>
+        <v>-18.59496695817187</v>
       </c>
       <c r="F46">
-        <v>-4.206492221116496</v>
+        <v>-4.31014181401722</v>
       </c>
       <c r="G46">
-        <v>-5.067949789461631</v>
+        <v>-5.747184349390518</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.298557056854516</v>
       </c>
       <c r="E47">
-        <v>-13.92430339513467</v>
+        <v>-17.46970003742788</v>
       </c>
       <c r="F47">
-        <v>-4.438626291230906</v>
+        <v>-4.646320611658255</v>
       </c>
       <c r="G47">
-        <v>-5.474365602044719</v>
+        <v>-5.27635525224983</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.714222861233996</v>
       </c>
       <c r="E48">
-        <v>-13.76341577059016</v>
+        <v>-17.09540807527191</v>
       </c>
       <c r="F48">
-        <v>-4.315377545773663</v>
+        <v>-4.68531620241412</v>
       </c>
       <c r="G48">
-        <v>-5.175770947130154</v>
+        <v>-6.445620073447178</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.051440722958473</v>
       </c>
       <c r="E49">
-        <v>-13.13585078565918</v>
+        <v>-15.39012514667749</v>
       </c>
       <c r="F49">
-        <v>-4.563412023279084</v>
+        <v>-4.784259021334157</v>
       </c>
       <c r="G49">
-        <v>-4.925692337093609</v>
+        <v>-5.261282338409528</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.313473142876734</v>
       </c>
       <c r="E50">
-        <v>-12.79743339459197</v>
+        <v>-15.02080997745594</v>
       </c>
       <c r="F50">
-        <v>-4.662491832760807</v>
+        <v>-4.773262559310304</v>
       </c>
       <c r="G50">
-        <v>-4.291855288144747</v>
+        <v>-5.731128203525053</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>5.499414583684662</v>
       </c>
       <c r="E51">
-        <v>-12.71727034770819</v>
+        <v>-15.62392120274549</v>
       </c>
       <c r="F51">
-        <v>-4.620137993611253</v>
+        <v>-4.745927795209819</v>
       </c>
       <c r="G51">
-        <v>-3.743142296647166</v>
+        <v>-5.134375885707107</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>5.617280506650014</v>
       </c>
       <c r="E52">
-        <v>-13.22641120886458</v>
+        <v>-15.63355779543382</v>
       </c>
       <c r="F52">
-        <v>-4.870916241615173</v>
+        <v>-4.738528721172885</v>
       </c>
       <c r="G52">
-        <v>-4.054360061702972</v>
+        <v>-5.029378623383582</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>5.670179068243991</v>
       </c>
       <c r="E53">
-        <v>-12.94762476353037</v>
+        <v>-16.28990123268353</v>
       </c>
       <c r="F53">
-        <v>-5.103305288381969</v>
+        <v>-4.801871414819759</v>
       </c>
       <c r="G53">
-        <v>-4.615689542250715</v>
+        <v>-4.738606787578315</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>5.66508131865187</v>
       </c>
       <c r="E54">
-        <v>-13.0760522863879</v>
+        <v>-14.11621106663172</v>
       </c>
       <c r="F54">
-        <v>-5.05927588837388</v>
+        <v>-5.033650734809111</v>
       </c>
       <c r="G54">
-        <v>-3.904670434599285</v>
+        <v>-5.18428235971162</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>5.60698745270015</v>
       </c>
       <c r="E55">
-        <v>-11.73017622588624</v>
+        <v>-15.42546988630736</v>
       </c>
       <c r="F55">
-        <v>-5.039911916145801</v>
+        <v>-5.250855209258674</v>
       </c>
       <c r="G55">
-        <v>-3.520206849487105</v>
+        <v>-4.430461208782953</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>5.499297983490677</v>
       </c>
       <c r="E56">
-        <v>-11.90923208814953</v>
+        <v>-12.37157117043664</v>
       </c>
       <c r="F56">
-        <v>-5.234119396997268</v>
+        <v>-5.429460019431231</v>
       </c>
       <c r="G56">
-        <v>-2.843316155800021</v>
+        <v>-4.793532048620364</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>5.346286179333833</v>
       </c>
       <c r="E57">
-        <v>-11.92402208425858</v>
+        <v>-13.07399183071441</v>
       </c>
       <c r="F57">
-        <v>-5.157213054037612</v>
+        <v>-5.219010842563975</v>
       </c>
       <c r="G57">
-        <v>-4.633662493983419</v>
+        <v>-4.324440987887793</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>5.148001558391715</v>
       </c>
       <c r="E58">
-        <v>-10.68098766847112</v>
+        <v>-14.10521140326709</v>
       </c>
       <c r="F58">
-        <v>-5.247254653859923</v>
+        <v>-5.390819178800424</v>
       </c>
       <c r="G58">
-        <v>-3.781862437274481</v>
+        <v>-5.298396864450298</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>4.907224127430478</v>
       </c>
       <c r="E59">
-        <v>-10.73556936568557</v>
+        <v>-12.83948027575319</v>
       </c>
       <c r="F59">
-        <v>-5.167682933844583</v>
+        <v>-5.769478512064249</v>
       </c>
       <c r="G59">
-        <v>-2.884439752488848</v>
+        <v>-4.857442130255993</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>4.624183643827288</v>
       </c>
       <c r="E60">
-        <v>-11.94092234925521</v>
+        <v>-13.50114014148791</v>
       </c>
       <c r="F60">
-        <v>-5.210147632408218</v>
+        <v>-5.256435397051725</v>
       </c>
       <c r="G60">
-        <v>-4.374632168808684</v>
+        <v>-5.504087679896295</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>4.303990252814965</v>
       </c>
       <c r="E61">
-        <v>-11.01438751033784</v>
+        <v>-12.88584279264372</v>
       </c>
       <c r="F61">
-        <v>-5.365515517536489</v>
+        <v>-5.722267446872041</v>
       </c>
       <c r="G61">
-        <v>-3.81543799013377</v>
+        <v>-5.28734957398575</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>3.953006012814303</v>
       </c>
       <c r="E62">
-        <v>-11.07540869759119</v>
+        <v>-11.69574170953192</v>
       </c>
       <c r="F62">
-        <v>-5.5120146495383</v>
+        <v>-5.766075919904927</v>
       </c>
       <c r="G62">
-        <v>-4.129115490525254</v>
+        <v>-5.426415660453915</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>3.581606373416536</v>
       </c>
       <c r="E63">
-        <v>-11.22715786158823</v>
+        <v>-11.96014119294376</v>
       </c>
       <c r="F63">
-        <v>-5.529220822456592</v>
+        <v>-5.48049731811514</v>
       </c>
       <c r="G63">
-        <v>-3.71713796143619</v>
+        <v>-6.067665020865205</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>3.203069398177221</v>
       </c>
       <c r="E64">
-        <v>-9.91025497778765</v>
+        <v>-12.67151011786068</v>
       </c>
       <c r="F64">
-        <v>-5.479853541660514</v>
+        <v>-6.007906229486616</v>
       </c>
       <c r="G64">
-        <v>-4.397971514860545</v>
+        <v>-5.817791664652094</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>2.830846393950731</v>
       </c>
       <c r="E65">
-        <v>-10.81484483166385</v>
+        <v>-13.99193162596522</v>
       </c>
       <c r="F65">
-        <v>-5.645604202770406</v>
+        <v>-5.728989486630124</v>
       </c>
       <c r="G65">
-        <v>-5.195988448738483</v>
+        <v>-4.76029417140608</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>2.480307477886434</v>
       </c>
       <c r="E66">
-        <v>-10.50658707748772</v>
+        <v>-13.15211706429474</v>
       </c>
       <c r="F66">
-        <v>-5.717898794104302</v>
+        <v>-5.610784052660597</v>
       </c>
       <c r="G66">
-        <v>-3.888269991997736</v>
+        <v>-6.353878235462895</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>2.163688413644858</v>
       </c>
       <c r="E67">
-        <v>-10.21359480919145</v>
+        <v>-12.92431217933888</v>
       </c>
       <c r="F67">
-        <v>-5.564676830491451</v>
+        <v>-5.818340590673302</v>
       </c>
       <c r="G67">
-        <v>-4.901657776478499</v>
+        <v>-6.075193201421507</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>1.895275408212802</v>
       </c>
       <c r="E68">
-        <v>-10.5936560472332</v>
+        <v>-13.25440623517999</v>
       </c>
       <c r="F68">
-        <v>-5.623627115781853</v>
+        <v>-6.329177603345619</v>
       </c>
       <c r="G68">
-        <v>-4.669091952344699</v>
+        <v>-6.344552428678768</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>1.682729354232382</v>
       </c>
       <c r="E69">
-        <v>-10.22804516974992</v>
+        <v>-11.53513937884989</v>
       </c>
       <c r="F69">
-        <v>-5.570699664087867</v>
+        <v>-6.210957916022854</v>
       </c>
       <c r="G69">
-        <v>-3.93181359747577</v>
+        <v>-6.053538923049135</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>1.535138518481808</v>
       </c>
       <c r="E70">
-        <v>-10.4221491511407</v>
+        <v>-12.11839777408982</v>
       </c>
       <c r="F70">
-        <v>-5.673129011580744</v>
+        <v>-5.986313191182557</v>
       </c>
       <c r="G70">
-        <v>-5.150471758119044</v>
+        <v>-5.435178674496366</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>1.452930246277643</v>
       </c>
       <c r="E71">
-        <v>-11.22170557888299</v>
+        <v>-11.96327036848306</v>
       </c>
       <c r="F71">
-        <v>-5.643885881852155</v>
+        <v>-6.202844986544537</v>
       </c>
       <c r="G71">
-        <v>-4.21693764259104</v>
+        <v>-6.63857190965806</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.438711359891534</v>
       </c>
       <c r="E72">
-        <v>-11.54493446812848</v>
+        <v>-13.22278842965844</v>
       </c>
       <c r="F72">
-        <v>-5.666822694625465</v>
+        <v>-6.134209547728264</v>
       </c>
       <c r="G72">
-        <v>-5.229822224149834</v>
+        <v>-5.412508058643437</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.488300720378575</v>
       </c>
       <c r="E73">
-        <v>-11.85833204030332</v>
+        <v>-12.66264336575366</v>
       </c>
       <c r="F73">
-        <v>-5.959456706268535</v>
+        <v>-5.818920227038353</v>
       </c>
       <c r="G73">
-        <v>-5.351484772718051</v>
+        <v>-7.345310481927212</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.597428420363355</v>
       </c>
       <c r="E74">
-        <v>-10.99077151838784</v>
+        <v>-13.58999785846642</v>
       </c>
       <c r="F74">
-        <v>-5.78124703072188</v>
+        <v>-6.118307160704857</v>
       </c>
       <c r="G74">
-        <v>-4.418867678304426</v>
+        <v>-5.928486375848705</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.756117438828163</v>
       </c>
       <c r="E75">
-        <v>-12.34119416679319</v>
+        <v>-13.15462583889498</v>
       </c>
       <c r="F75">
-        <v>-5.744762405694943</v>
+        <v>-6.13611039075327</v>
       </c>
       <c r="G75">
-        <v>-4.988625807795153</v>
+        <v>-6.225452242357948</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.954187490824671</v>
       </c>
       <c r="E76">
-        <v>-12.98026600417765</v>
+        <v>-14.73748147269204</v>
       </c>
       <c r="F76">
-        <v>-5.929459732524196</v>
+        <v>-6.752548122014132</v>
       </c>
       <c r="G76">
-        <v>-4.614411671672556</v>
+        <v>-5.867900081934502</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>2.177605895585344</v>
       </c>
       <c r="E77">
-        <v>-12.57484531169295</v>
+        <v>-14.34919652585236</v>
       </c>
       <c r="F77">
-        <v>-6.113177537244749</v>
+        <v>-6.290873300221843</v>
       </c>
       <c r="G77">
-        <v>-4.971268617532755</v>
+        <v>-6.799222753042272</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>2.4139591148366</v>
       </c>
       <c r="E78">
-        <v>-12.9257975188134</v>
+        <v>-15.38603593464856</v>
       </c>
       <c r="F78">
-        <v>-6.254634149611801</v>
+        <v>-6.669234104920609</v>
       </c>
       <c r="G78">
-        <v>-4.288233551324784</v>
+        <v>-6.288005000322477</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>2.648397656634585</v>
       </c>
       <c r="E79">
-        <v>-14.46748479540671</v>
+        <v>-15.51790056927791</v>
       </c>
       <c r="F79">
-        <v>-6.400299064522653</v>
+        <v>-6.111307180558615</v>
       </c>
       <c r="G79">
-        <v>-4.518597862674969</v>
+        <v>-5.736405213114651</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.869737339725791</v>
       </c>
       <c r="E80">
-        <v>-13.77177533360832</v>
+        <v>-15.6296542508392</v>
       </c>
       <c r="F80">
-        <v>-6.678874122827889</v>
+        <v>-6.68351636079252</v>
       </c>
       <c r="G80">
-        <v>-4.99045985002391</v>
+        <v>-6.011485063063772</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.064594280858537</v>
       </c>
       <c r="E81">
-        <v>-14.78850831781047</v>
+        <v>-16.71486681898534</v>
       </c>
       <c r="F81">
-        <v>-6.560958111114408</v>
+        <v>-6.636688552431849</v>
       </c>
       <c r="G81">
-        <v>-5.230772350719605</v>
+        <v>-5.82493913247138</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.221936296113351</v>
       </c>
       <c r="E82">
-        <v>-15.77161285403165</v>
+        <v>-17.36522361359692</v>
       </c>
       <c r="F82">
-        <v>-6.48860531858812</v>
+        <v>-6.689781501393999</v>
       </c>
       <c r="G82">
-        <v>-4.541251925800203</v>
+        <v>-6.510877547117292</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.331128920275172</v>
       </c>
       <c r="E83">
-        <v>-17.31610325603572</v>
+        <v>-18.42853648144197</v>
       </c>
       <c r="F83">
-        <v>-6.261309865971857</v>
+        <v>-6.615776903597908</v>
       </c>
       <c r="G83">
-        <v>-5.131760554731083</v>
+        <v>-6.440204020944931</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.384642399225524</v>
       </c>
       <c r="E84">
-        <v>-17.84059564407811</v>
+        <v>-19.06677960808303</v>
       </c>
       <c r="F84">
-        <v>-6.296640365312916</v>
+        <v>-6.643899957317803</v>
       </c>
       <c r="G84">
-        <v>-4.822701265366882</v>
+        <v>-6.592922797217049</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.37934963558623</v>
       </c>
       <c r="E85">
-        <v>-18.4989270814172</v>
+        <v>-18.54166681910159</v>
       </c>
       <c r="F85">
-        <v>-6.787627999894073</v>
+        <v>-7.044853910606228</v>
       </c>
       <c r="G85">
-        <v>-4.540417668324306</v>
+        <v>-6.460706229469637</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.313241918783746</v>
       </c>
       <c r="E86">
-        <v>-19.99736290276326</v>
+        <v>-21.85577165145304</v>
       </c>
       <c r="F86">
-        <v>-6.625446220064624</v>
+        <v>-7.137650366868444</v>
       </c>
       <c r="G86">
-        <v>-4.573860799362023</v>
+        <v>-6.645563781837001</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.187922268172171</v>
       </c>
       <c r="E87">
-        <v>-21.43677912236735</v>
+        <v>-23.04304243831005</v>
       </c>
       <c r="F87">
-        <v>-6.705362000190092</v>
+        <v>-7.113805694679109</v>
       </c>
       <c r="G87">
-        <v>-4.408472565311114</v>
+        <v>-6.512499714431534</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.003984489802269</v>
       </c>
       <c r="E88">
-        <v>-23.61574496063809</v>
+        <v>-23.84857192326846</v>
       </c>
       <c r="F88">
-        <v>-6.985197688404018</v>
+        <v>-6.985316466347675</v>
       </c>
       <c r="G88">
-        <v>-4.880781476307855</v>
+        <v>-5.733485311949014</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.764123506856096</v>
       </c>
       <c r="E89">
-        <v>-24.82070849544307</v>
+        <v>-25.07038138138197</v>
       </c>
       <c r="F89">
-        <v>-6.779488939268151</v>
+        <v>-6.906248364813446</v>
       </c>
       <c r="G89">
-        <v>-4.425502011565125</v>
+        <v>-5.986808256614045</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.471600973175183</v>
       </c>
       <c r="E90">
-        <v>-25.78945776905994</v>
+        <v>-26.59930288974766</v>
       </c>
       <c r="F90">
-        <v>-6.806991972122152</v>
+        <v>-6.972585054493457</v>
       </c>
       <c r="G90">
-        <v>-4.395392599885453</v>
+        <v>-5.720382172704578</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.12860776471577</v>
       </c>
       <c r="E91">
-        <v>-27.20873586475193</v>
+        <v>-29.02059642911686</v>
       </c>
       <c r="F91">
-        <v>-6.590713173780164</v>
+        <v>-6.627089710878371</v>
       </c>
       <c r="G91">
-        <v>-4.791787391121168</v>
+        <v>-5.841223705979055</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.739002400987304</v>
       </c>
       <c r="E92">
-        <v>-29.26703598461429</v>
+        <v>-30.84519106239138</v>
       </c>
       <c r="F92">
-        <v>-6.794137823059487</v>
+        <v>-6.904227556065345</v>
       </c>
       <c r="G92">
-        <v>-4.816725730668497</v>
+        <v>-6.492570230285122</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.299474680973963</v>
       </c>
       <c r="E93">
-        <v>-31.04582510330121</v>
+        <v>-32.40078075418824</v>
       </c>
       <c r="F93">
-        <v>-6.792265882667437</v>
+        <v>-6.702073830783161</v>
       </c>
       <c r="G93">
-        <v>-5.432003861324205</v>
+        <v>-6.185497268244484</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.8129712426875311</v>
       </c>
       <c r="E94">
-        <v>-32.98628300829897</v>
+        <v>-34.64600043142821</v>
       </c>
       <c r="F94">
-        <v>-6.857136456596232</v>
+        <v>-6.670549372683381</v>
       </c>
       <c r="G94">
-        <v>-5.188725111825322</v>
+        <v>-5.511559581178431</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.2743426856624573</v>
       </c>
       <c r="E95">
-        <v>-36.46486654508302</v>
+        <v>-36.62562963659231</v>
       </c>
       <c r="F95">
-        <v>-6.57171899688334</v>
+        <v>-6.781814611404974</v>
       </c>
       <c r="G95">
-        <v>-6.074759519955863</v>
+        <v>-7.87323324743817</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.3173337971706283</v>
       </c>
       <c r="E96">
-        <v>-38.09139704644704</v>
+        <v>-38.94865528999507</v>
       </c>
       <c r="F96">
-        <v>-6.742104373354766</v>
+        <v>-6.731530760810335</v>
       </c>
       <c r="G96">
-        <v>-6.533170760778744</v>
+        <v>-6.667863616589531</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.9585867195293848</v>
       </c>
       <c r="E97">
-        <v>-39.73479384925264</v>
+        <v>-40.78163439289479</v>
       </c>
       <c r="F97">
-        <v>-6.48101422020894</v>
+        <v>-6.795802297976614</v>
       </c>
       <c r="G97">
-        <v>-6.423244096147244</v>
+        <v>-7.857948458683356</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.655639006389693</v>
       </c>
       <c r="E98">
-        <v>-41.8158835145586</v>
+        <v>-43.27108373031643</v>
       </c>
       <c r="F98">
-        <v>-6.313573348960795</v>
+        <v>-6.929263571029569</v>
       </c>
       <c r="G98">
-        <v>-7.069806882149064</v>
+        <v>-8.822671223736833</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.381836743372718</v>
       </c>
       <c r="E99">
-        <v>-44.54063915412981</v>
+        <v>-45.55021941363685</v>
       </c>
       <c r="F99">
-        <v>-6.643610535061756</v>
+        <v>-6.3607020614454</v>
       </c>
       <c r="G99">
-        <v>-7.342258158940004</v>
+        <v>-8.201460595474751</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.156214869016446</v>
       </c>
       <c r="E100">
-        <v>-47.07249765063329</v>
+        <v>-46.89205381108665</v>
       </c>
       <c r="F100">
-        <v>-6.350210009755613</v>
+        <v>-6.667370874911094</v>
       </c>
       <c r="G100">
-        <v>-8.862242174567742</v>
+        <v>-9.00937937106065</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.902730303260625</v>
       </c>
       <c r="E101">
-        <v>-49.17812711658681</v>
+        <v>-49.09046265250933</v>
       </c>
       <c r="F101">
-        <v>-6.417831480859526</v>
+        <v>-5.916437710634495</v>
       </c>
       <c r="G101">
-        <v>-8.867539047430576</v>
+        <v>-9.319683425547616</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.694510305372043</v>
       </c>
       <c r="E102">
-        <v>-52.15898947154332</v>
+        <v>-51.94581042551373</v>
       </c>
       <c r="F102">
-        <v>-5.907786717071407</v>
+        <v>-5.925682593915873</v>
       </c>
       <c r="G102">
-        <v>-9.087809505431522</v>
+        <v>-9.615944145856995</v>
       </c>
     </row>
   </sheetData>
